--- a/peer_review/20260515_du_jufe_dm_peer_review_vector.xlsx
+++ b/peer_review/20260515_du_jufe_dm_peer_review_vector.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpi\source\20260512_du_jufe_dm\20260512_du_jufe_dm_rpi\peer_review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4200A8F0-AD6D-4342-A92D-6FECEF8502E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A956C518-1ABC-4957-9DEB-A58B6B82C764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
